--- a/public/templates/daily-accomplishment-report.xlsx
+++ b/public/templates/daily-accomplishment-report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOST\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BD41D3-DDE3-450B-9234-26A19A3AAD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59FCFE8-FD64-4446-B126-DEB219609D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55F3A54E-E2BF-45B5-BC3E-3693EAB1DD7B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{55F3A54E-E2BF-45B5-BC3E-3693EAB1DD7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>No.</t>
   </si>
@@ -100,12 +100,15 @@
       <t xml:space="preserve"> </t>
     </r>
   </si>
+  <si>
+    <t>DIVISION CHIEF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +132,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -138,7 +148,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,24 +171,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7498B116-370D-40A6-8B69-077D7B2BD167}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -524,60 +550,82 @@
     <col min="5" max="5" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+    <row r="9" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="13" spans="1:6" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="6"/>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
